--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -420,9 +420,9 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
@@ -431,7 +431,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MF001</t>
+          <t>MF1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -588,27 +588,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>123 Main St</t>
+          <t>123 Street</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gauteng</t>
+          <t>Western Cape</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>123 Main St, Johannesburg, Gauteng, 2000, South Africa</t>
+          <t>123 Street, Cape Town, Western Cape, 8000, South Africa</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -626,27 +626,27 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Hope Church</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>456 Church St</t>
+          <t>1 Road</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Gauteng</t>
+          <t>Western Cape</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -656,32 +656,32 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>456 Church St, Johannesburg, Gauteng, 2001, South Africa</t>
+          <t>1 Road, Cape Town, Western Cape, 8000, South Africa</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Pastor M</t>
+          <t>Pastor</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Kin</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Doe</t>
+          <t>Surname</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0821234567</t>
+          <t>123</t>
         </is>
       </c>
     </row>
